--- a/data/Brew Design Ingredients.xlsx
+++ b/data/Brew Design Ingredients.xlsx
@@ -1,192 +1,206 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2435ABB5-7B24-4E84-B2AD-4B63706FD5A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="6" name="Read Me" state="visible" r:id="rId4"/>
-    <sheet sheetId="1" name="Malts" state="visible" r:id="rId5"/>
-    <sheet sheetId="2" name="Hops" state="visible" r:id="rId6"/>
-    <sheet sheetId="3" name="Yeasts" state="visible" r:id="rId7"/>
-    <sheet sheetId="4" name="Yeast Packs" state="visible" r:id="rId8"/>
-    <sheet sheetId="5" name="Review" state="visible" r:id="rId9"/>
+    <sheet name="Read Me" sheetId="6" r:id="rId1"/>
+    <sheet name="Malts" sheetId="1" r:id="rId2"/>
+    <sheet name="Hops" sheetId="2" r:id="rId3"/>
+    <sheet name="Yeasts" sheetId="3" r:id="rId4"/>
+    <sheet name="Yeast Packs" sheetId="4" r:id="rId5"/>
+    <sheet name="Review" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="171027" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>The name shown in the app's search box. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Optional: who makes it (Rahr, Weyermann, Briess ...).</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Extract, fine grind dry basis. Used by the app. Type it with the % sign (82%).</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Degrees Lovibond. Used by the app.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Price paid for one pack.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Size of that pack, in the unit in the next column.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>lb or oz.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Where you buy it.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Computed: price ÷ pack size in pounds. Do not type here.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>How many of your recipe workbooks list it (seeded rows).</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Where the numbers came from. Replace with the maltster spec sheet or link when you confirm a row.</t>
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="0">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Check = see Notes and the Review sheet. OK = seeded, no disagreement. Confirmed = you checked it.</t>
         </r>
@@ -197,160 +211,160 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>The name shown in the app's search box. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Optional: country or grower.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Used by the app. Type it with the % sign (12.5%). Alpha changes with every crop year and lot: this is the typical figure the app fills in, and the brewer can overwrite it.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Price paid for one pack.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Size of that pack, in the unit in the next column.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>lb or oz.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Where you buy it.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Computed: price ÷ pack size in ounces. Do not type here.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>How many of your recipe workbooks list it (seeded rows).</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000A000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Where the number came from. Replace with the merchant's variety page or lot sheet when you confirm a row.</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-00000B000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Check = see Notes and the Review sheet. OK = seeded, no disagreement. Confirmed = you checked it.</t>
         </r>
@@ -361,146 +375,146 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>The name shown in the app's search box: product code and strain name. Required.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Imperial, Omega, White Labs, Wyeast ...</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Used by the app to pick the pitch rate. Ale or Lager only; wheat (hefeweizen) strains are ales.</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Apparent attenuation. Used by the app. Seeded from what you entered in your recipes, which is a target, not the lab spec; replace with the lab figure when you confirm.</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Lab's recommended fermentation range, low end. Shown in the app as guidance.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Lab's recommended fermentation range, high end.</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>The initial fermentation temperature you used most often with this strain (from your recipes). For reference.</t>
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>How many of your recipe workbooks used it.</t>
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Where the numbers came from. Replace with the lab's product page when you confirm a row.</t>
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Check = see Notes and the Review sheet. OK = seeded. Confirmed = you checked it.</t>
         </r>
@@ -511,48 +525,48 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Pack family; price depends on the pack, not the strain.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Cells per pack, billions.</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Computed: price ÷ cells. Do not type here.</t>
         </r>
@@ -563,20 +577,20 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
       <text>
         <r>
           <rPr>
+            <sz val="11"/>
             <color theme="1"/>
+            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
           </rPr>
           <t>Write what you want, or leave blank to accept the seed.</t>
         </r>
@@ -587,7 +601,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="475">
   <si>
     <t>Brew Design — ingredient master list</t>
   </si>
@@ -1663,7 +1677,7 @@
     <t>FGDB differs across your workbooks</t>
   </si>
   <si>
-    <t xml:space="preserve">70% in 30 (latest 2026-09-22)
+    <t>70% in 30 (latest 2026-09-22)
 79% in 1 (latest 2023-03-31)</t>
   </si>
   <si>
@@ -1673,7 +1687,7 @@
     <t>79% per Briess</t>
   </si>
   <si>
-    <t xml:space="preserve">92% in 19 (latest 2026-09-22)
+    <t>92% in 19 (latest 2026-09-22)
 100% in 1 (latest 2025-02-13)</t>
   </si>
   <si>
@@ -1701,7 +1715,7 @@
     <t>use $0.995/lb</t>
   </si>
   <si>
-    <t xml:space="preserve">81% in 36 (latest 2026-09-22)
+    <t>81% in 36 (latest 2026-09-22)
 80% in 8 (latest 2026-06-16)
 79.6% in 1 (latest 2023-11-01)</t>
   </si>
@@ -1715,7 +1729,7 @@
     <t>Colour differs across your workbooks</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2 °L in 39 (latest 2026-09-22)
+    <t>2.2 °L in 39 (latest 2026-09-22)
 1.9 °L in 6 (latest 2024-06-05)</t>
   </si>
   <si>
@@ -1734,7 +1748,7 @@
     <t>Also written as: Lactose (added in kettle)</t>
   </si>
   <si>
-    <t xml:space="preserve">0% in 44 (latest 2026-09-22)
+    <t>0% in 44 (latest 2026-09-22)
 70% in 1 (latest 2023-01-09)</t>
   </si>
   <si>
@@ -1759,7 +1773,7 @@
     <t>good as written</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3 °L in 37 (latest 2026-09-22)
+    <t>3.3 °L in 37 (latest 2026-09-22)
 2.75 °L in 5 (latest 2026-06-16)</t>
   </si>
   <si>
@@ -1784,7 +1798,7 @@
     <t>Alpha acid differs across your workbooks</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2% in 39 (latest 2026-09-22)
+    <t>14.2% in 39 (latest 2026-09-22)
 14.7% in 6 (latest 2026-09-22)</t>
   </si>
   <si>
@@ -1794,7 +1808,7 @@
     <t>14.4% is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2% in 1 (latest 2026-09-22)
+    <t>6.2% in 1 (latest 2026-09-22)
 10% in 1 (latest 2025-10-29)
 5% in 1 (latest 2025-08-18)
 5.75% in 1 (latest 2024-12-26)</t>
@@ -1806,7 +1820,7 @@
     <t>6.2% is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5% in 40 (latest 2026-09-22)
+    <t>5.5% in 40 (latest 2026-09-22)
 4.8% in 3 (latest 2025-04-07)
 4.2% in 2 (latest 2023-11-01)</t>
   </si>
@@ -1817,7 +1831,7 @@
     <t>5.5% is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">5% in 41 (latest 2026-09-22)
+    <t>5% in 41 (latest 2026-09-22)
 4.6% in 2 (latest 2023-11-01)
 5.6% in 1 (latest 2023-11-04)
 4.4% in 1 (latest 2023-03-31)</t>
@@ -1829,7 +1843,7 @@
     <t>5% is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">15% in 8 (latest 2026-09-22)
+    <t>15% in 8 (latest 2026-09-22)
 15.5% in 1 (latest 2025-10-29)</t>
   </si>
   <si>
@@ -1839,7 +1853,7 @@
     <t>15% is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5% in 33 (latest 2026-09-22)
+    <t>10.5% in 33 (latest 2026-09-22)
 9.3% in 1 (latest 2025-02-13)</t>
   </si>
   <si>
@@ -1849,7 +1863,7 @@
     <t>10.5% is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2% in 41 (latest 2026-09-22)
+    <t>4.2% in 41 (latest 2026-09-22)
 2.9% in 2 (latest 2026-01-22)
 2.8% in 2 (latest 2024-06-22)</t>
   </si>
@@ -1866,7 +1880,7 @@
     <t>ok</t>
   </si>
   <si>
-    <t xml:space="preserve">7% in 33 (latest 2026-09-22)
+    <t>7% in 33 (latest 2026-09-22)
 9.1% in 1 (latest 2025-02-13)</t>
   </si>
   <si>
@@ -1876,7 +1890,7 @@
     <t>use 7%</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9% in 25 (latest 2026-09-22)
+    <t>4.9% in 25 (latest 2026-09-22)
 6% in 1 (latest 2023-03-09)</t>
   </si>
   <si>
@@ -1895,7 +1909,7 @@
     <t>use $2</t>
   </si>
   <si>
-    <t xml:space="preserve">9% in 1 (latest 2026-09-22)
+    <t>9% in 1 (latest 2026-09-22)
 11% in 1 (latest 2026-07-05)
 12% in 1 (latest 2024-12-26)</t>
   </si>
@@ -1906,7 +1920,7 @@
     <t>9% is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5% in 32 (latest 2026-09-22)
+    <t>12.5% in 32 (latest 2026-09-22)
 11.7% in 1 (latest 2025-02-21)
 9.6% in 1 (latest 2025-02-13)</t>
   </si>
@@ -1917,7 +1931,7 @@
     <t>12.5 is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5% in 44 (latest 2026-09-22)
+    <t>9.5% in 44 (latest 2026-09-22)
 7.8% in 1 (latest 2024-02-06)</t>
   </si>
   <si>
@@ -1927,7 +1941,7 @@
     <t>9.5 is fine</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6% in 2 (latest 2026-01-22)
+    <t>2.6% in 2 (latest 2026-01-22)
 3% in 1 (latest 2025-04-27)</t>
   </si>
   <si>
@@ -2019,75 +2033,103 @@
   </si>
   <si>
     <t>Also written as: WLP 830, WLP 830 German Lager, 830 German lager</t>
+  </si>
+  <si>
+    <t>Malt type</t>
+  </si>
+  <si>
+    <t>Distilled-water pH</t>
+  </si>
+  <si>
+    <t>Acidity (mEq/kg)</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>crystal</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>roast</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0#%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="$#,##0.000"/>
-    <numFmt numFmtId="167" formatCode="$#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0.0000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <family val="2"/>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2104,6 +2146,11 @@
         <fgColor rgb="FFDDE6EF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2117,7 +2164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2154,6 +2201,10 @@
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2492,9 +2543,174 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M43"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -2505,9 +2721,10 @@
     <col min="11" max="11" width="38" customWidth="1"/>
     <col min="12" max="12" width="11" customWidth="1"/>
     <col min="13" max="13" width="60" customWidth="1"/>
+    <col min="14" max="16" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.9" customHeight="1" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" s="6" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
@@ -2547,8 +2764,17 @@
       <c r="M1" s="6" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="2" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" s="14" t="s">
+        <v>468</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>469</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>44</v>
       </c>
@@ -2559,10 +2785,10 @@
         <v>0.82</v>
       </c>
       <c r="D2" s="7">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E2" s="9">
-        <v>64.99</v>
+        <v>64.989999999999995</v>
       </c>
       <c r="F2" s="7">
         <v>55</v>
@@ -2574,7 +2800,7 @@
         <v>46</v>
       </c>
       <c r="I2" s="10">
-        <f>IF(OR(E2="",F2=""),"",E2/IF(G2="oz",F2/16,F2))</f>
+        <f t="shared" ref="I2:I43" si="0">IF(OR(E2="",F2=""),"",E2/IF(G2="oz",F2/16,F2))</f>
         <v>1.1816363636363636</v>
       </c>
       <c r="J2" s="7">
@@ -2589,8 +2815,13 @@
       <c r="M2" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+    </row>
+    <row r="3" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>49</v>
       </c>
@@ -2604,7 +2835,7 @@
         <v>120</v>
       </c>
       <c r="E3" s="9">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="F3" s="7">
         <v>1</v>
@@ -2616,8 +2847,8 @@
         <v>46</v>
       </c>
       <c r="I3" s="10">
-        <f>IF(OR(E3="",F3=""),"",E3/IF(G3="oz",F3/16,F3))</f>
-        <v>2.49</v>
+        <f t="shared" si="0"/>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J3" s="7">
         <v>45</v>
@@ -2631,8 +2862,13 @@
       <c r="M3" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N3" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
+    </row>
+    <row r="4" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>50</v>
       </c>
@@ -2646,7 +2882,7 @@
         <v>40</v>
       </c>
       <c r="E4" s="9">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="F4" s="7">
         <v>1</v>
@@ -2658,8 +2894,8 @@
         <v>46</v>
       </c>
       <c r="I4" s="10">
-        <f>IF(OR(E4="",F4=""),"",E4/IF(G4="oz",F4/16,F4))</f>
-        <v>2.49</v>
+        <f t="shared" si="0"/>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J4" s="7">
         <v>45</v>
@@ -2673,8 +2909,13 @@
       <c r="M4" s="7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N4" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+    </row>
+    <row r="5" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>53</v>
       </c>
@@ -2688,7 +2929,7 @@
         <v>60</v>
       </c>
       <c r="E5" s="9">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="F5" s="7">
         <v>1</v>
@@ -2700,8 +2941,8 @@
         <v>46</v>
       </c>
       <c r="I5" s="10">
-        <f>IF(OR(E5="",F5=""),"",E5/IF(G5="oz",F5/16,F5))</f>
-        <v>2.49</v>
+        <f t="shared" si="0"/>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J5" s="7">
         <v>45</v>
@@ -2715,8 +2956,13 @@
       <c r="M5" s="7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="6" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N5" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+    </row>
+    <row r="6" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>55</v>
       </c>
@@ -2742,7 +2988,7 @@
         <v>56</v>
       </c>
       <c r="I6" s="10">
-        <f>IF(OR(E6="",F6=""),"",E6/IF(G6="oz",F6/16,F6))</f>
+        <f t="shared" si="0"/>
         <v>2.59</v>
       </c>
       <c r="J6" s="7">
@@ -2757,8 +3003,13 @@
       <c r="M6" s="7" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="7" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N6" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+    </row>
+    <row r="7" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>59</v>
       </c>
@@ -2784,7 +3035,7 @@
         <v>46</v>
       </c>
       <c r="I7" s="10">
-        <f>IF(OR(E7="",F7=""),"",E7/IF(G7="oz",F7/16,F7))</f>
+        <f t="shared" si="0"/>
         <v>2.69</v>
       </c>
       <c r="J7" s="7">
@@ -2799,8 +3050,15 @@
       <c r="M7" s="7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N7" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>62</v>
       </c>
@@ -2826,7 +3084,7 @@
         <v>46</v>
       </c>
       <c r="I8" s="10">
-        <f>IF(OR(E8="",F8=""),"",E8/IF(G8="oz",F8/16,F8))</f>
+        <f t="shared" si="0"/>
         <v>5.99</v>
       </c>
       <c r="J8" s="7">
@@ -2841,8 +3099,13 @@
       <c r="M8" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N8" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="O8" s="15"/>
+      <c r="P8" s="15"/>
+    </row>
+    <row r="9" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>64</v>
       </c>
@@ -2868,8 +3131,8 @@
         <v>46</v>
       </c>
       <c r="I9" s="10">
-        <f>IF(OR(E9="",F9=""),"",E9/IF(G9="oz",F9/16,F9))</f>
-        <v>1.1</v>
+        <f t="shared" si="0"/>
+        <v>1.1000000000000001</v>
       </c>
       <c r="J9" s="7">
         <v>45</v>
@@ -2883,8 +3146,13 @@
       <c r="M9" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N9" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O9" s="15"/>
+      <c r="P9" s="15"/>
+    </row>
+    <row r="10" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>65</v>
       </c>
@@ -2910,7 +3178,7 @@
         <v>46</v>
       </c>
       <c r="I10" s="10">
-        <f>IF(OR(E10="",F10=""),"",E10/IF(G10="oz",F10/16,F10))</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="J10" s="7">
@@ -2925,8 +3193,13 @@
       <c r="M10" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N10" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="O10" s="15"/>
+      <c r="P10" s="15"/>
+    </row>
+    <row r="11" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>67</v>
       </c>
@@ -2952,7 +3225,7 @@
         <v>46</v>
       </c>
       <c r="I11" s="10">
-        <f>IF(OR(E11="",F11=""),"",E11/IF(G11="oz",F11/16,F11))</f>
+        <f t="shared" si="0"/>
         <v>2.99</v>
       </c>
       <c r="J11" s="7">
@@ -2967,8 +3240,13 @@
       <c r="M11" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N11" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+    </row>
+    <row r="12" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>69</v>
       </c>
@@ -2994,7 +3272,7 @@
         <v>46</v>
       </c>
       <c r="I12" s="10">
-        <f>IF(OR(E12="",F12=""),"",E12/IF(G12="oz",F12/16,F12))</f>
+        <f t="shared" si="0"/>
         <v>2.99</v>
       </c>
       <c r="J12" s="7">
@@ -3009,8 +3287,13 @@
       <c r="M12" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N12" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+    </row>
+    <row r="13" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>71</v>
       </c>
@@ -3036,7 +3319,7 @@
         <v>72</v>
       </c>
       <c r="I13" s="10">
-        <f>IF(OR(E13="",F13=""),"",E13/IF(G13="oz",F13/16,F13))</f>
+        <f t="shared" si="0"/>
         <v>2.5</v>
       </c>
       <c r="J13" s="7">
@@ -3051,8 +3334,13 @@
       <c r="M13" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N13" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+    </row>
+    <row r="14" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>74</v>
       </c>
@@ -3078,7 +3366,7 @@
         <v>46</v>
       </c>
       <c r="I14" s="10">
-        <f>IF(OR(E14="",F14=""),"",E14/IF(G14="oz",F14/16,F14))</f>
+        <f t="shared" si="0"/>
         <v>3.19</v>
       </c>
       <c r="J14" s="7">
@@ -3093,8 +3381,13 @@
       <c r="M14" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N14" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+    </row>
+    <row r="15" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>76</v>
       </c>
@@ -3120,7 +3413,7 @@
         <v>56</v>
       </c>
       <c r="I15" s="10">
-        <f>IF(OR(E15="",F15=""),"",E15/IF(G15="oz",F15/16,F15))</f>
+        <f t="shared" si="0"/>
         <v>3.49</v>
       </c>
       <c r="J15" s="7">
@@ -3135,8 +3428,13 @@
       <c r="M15" s="7" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="16" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N15" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+    </row>
+    <row r="16" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>79</v>
       </c>
@@ -3162,7 +3460,7 @@
         <v>46</v>
       </c>
       <c r="I16" s="10">
-        <f>IF(OR(E16="",F16=""),"",E16/IF(G16="oz",F16/16,F16))</f>
+        <f t="shared" si="0"/>
         <v>3.15</v>
       </c>
       <c r="J16" s="7">
@@ -3177,8 +3475,13 @@
       <c r="M16" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N16" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+    </row>
+    <row r="17" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>80</v>
       </c>
@@ -3204,7 +3507,7 @@
         <v>46</v>
       </c>
       <c r="I17" s="10">
-        <f>IF(OR(E17="",F17=""),"",E17/IF(G17="oz",F17/16,F17))</f>
+        <f t="shared" si="0"/>
         <v>2.89</v>
       </c>
       <c r="J17" s="7">
@@ -3219,8 +3522,13 @@
       <c r="M17" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N17" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+    </row>
+    <row r="18" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>81</v>
       </c>
@@ -3246,7 +3554,7 @@
         <v>46</v>
       </c>
       <c r="I18" s="10">
-        <f>IF(OR(E18="",F18=""),"",E18/IF(G18="oz",F18/16,F18))</f>
+        <f t="shared" si="0"/>
         <v>2.99</v>
       </c>
       <c r="J18" s="7">
@@ -3261,8 +3569,13 @@
       <c r="M18" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N18" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+    </row>
+    <row r="19" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>82</v>
       </c>
@@ -3288,7 +3601,7 @@
         <v>46</v>
       </c>
       <c r="I19" s="10">
-        <f>IF(OR(E19="",F19=""),"",E19/IF(G19="oz",F19/16,F19))</f>
+        <f t="shared" si="0"/>
         <v>2.99</v>
       </c>
       <c r="J19" s="7">
@@ -3303,8 +3616,13 @@
       <c r="M19" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N19" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+    </row>
+    <row r="20" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>83</v>
       </c>
@@ -3330,7 +3648,7 @@
         <v>46</v>
       </c>
       <c r="I20" s="10">
-        <f>IF(OR(E20="",F20=""),"",E20/IF(G20="oz",F20/16,F20))</f>
+        <f t="shared" si="0"/>
         <v>3.25</v>
       </c>
       <c r="J20" s="7">
@@ -3345,8 +3663,13 @@
       <c r="M20" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N20" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+    </row>
+    <row r="21" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>85</v>
       </c>
@@ -3372,7 +3695,7 @@
         <v>46</v>
       </c>
       <c r="I21" s="10">
-        <f>IF(OR(E21="",F21=""),"",E21/IF(G21="oz",F21/16,F21))</f>
+        <f t="shared" si="0"/>
         <v>1.99</v>
       </c>
       <c r="J21" s="7">
@@ -3387,8 +3710,13 @@
       <c r="M21" s="7" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="22" ht="41.45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N21" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+    </row>
+    <row r="22" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>88</v>
       </c>
@@ -3414,8 +3742,8 @@
         <v>56</v>
       </c>
       <c r="I22" s="10">
-        <f>IF(OR(E22="",F22=""),"",E22/IF(G22="oz",F22/16,F22))</f>
-        <v>2.2</v>
+        <f t="shared" si="0"/>
+        <v>2.2000000000000002</v>
       </c>
       <c r="J22" s="7">
         <v>1</v>
@@ -3429,8 +3757,13 @@
       <c r="M22" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N22" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+    </row>
+    <row r="23" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>90</v>
       </c>
@@ -3456,7 +3789,7 @@
         <v>46</v>
       </c>
       <c r="I23" s="10">
-        <f>IF(OR(E23="",F23=""),"",E23/IF(G23="oz",F23/16,F23))</f>
+        <f t="shared" si="0"/>
         <v>0.995</v>
       </c>
       <c r="J23" s="7">
@@ -3471,8 +3804,13 @@
       <c r="M23" s="7" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="24" ht="41.45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N23" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+    </row>
+    <row r="24" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>92</v>
       </c>
@@ -3483,7 +3821,7 @@
         <v>0.81</v>
       </c>
       <c r="D24" s="7">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E24" s="9">
         <v>84.99</v>
@@ -3498,7 +3836,7 @@
         <v>46</v>
       </c>
       <c r="I24" s="10">
-        <f>IF(OR(E24="",F24=""),"",E24/IF(G24="oz",F24/16,F24))</f>
+        <f t="shared" si="0"/>
         <v>1.5452727272727271</v>
       </c>
       <c r="J24" s="7">
@@ -3513,8 +3851,13 @@
       <c r="M24" s="7" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="25" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N24" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+    </row>
+    <row r="25" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>94</v>
       </c>
@@ -3540,7 +3883,7 @@
         <v>46</v>
       </c>
       <c r="I25" s="10">
-        <f>IF(OR(E25="",F25=""),"",E25/IF(G25="oz",F25/16,F25))</f>
+        <f t="shared" si="0"/>
         <v>1.99</v>
       </c>
       <c r="J25" s="7">
@@ -3555,8 +3898,13 @@
       <c r="M25" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N25" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O25" s="15"/>
+      <c r="P25" s="15"/>
+    </row>
+    <row r="26" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>95</v>
       </c>
@@ -3570,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="9">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="F26" s="7">
         <v>1</v>
@@ -3582,8 +3930,8 @@
         <v>46</v>
       </c>
       <c r="I26" s="10">
-        <f>IF(OR(E26="",F26=""),"",E26/IF(G26="oz",F26/16,F26))</f>
-        <v>2.49</v>
+        <f t="shared" si="0"/>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J26" s="7">
         <v>1</v>
@@ -3597,8 +3945,13 @@
       <c r="M26" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N26" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O26" s="15"/>
+      <c r="P26" s="15"/>
+    </row>
+    <row r="27" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>97</v>
       </c>
@@ -3624,7 +3977,7 @@
         <v>46</v>
       </c>
       <c r="I27" s="10">
-        <f>IF(OR(E27="",F27=""),"",E27/IF(G27="oz",F27/16,F27))</f>
+        <f t="shared" si="0"/>
         <v>5.49</v>
       </c>
       <c r="J27" s="7">
@@ -3639,8 +3992,13 @@
       <c r="M27" s="7" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="28" ht="55.15" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N27" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+    </row>
+    <row r="28" spans="1:16" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>99</v>
       </c>
@@ -3666,7 +4024,7 @@
         <v>46</v>
       </c>
       <c r="I28" s="10">
-        <f>IF(OR(E28="",F28=""),"",E28/IF(G28="oz",F28/16,F28))</f>
+        <f t="shared" si="0"/>
         <v>2.79</v>
       </c>
       <c r="J28" s="7">
@@ -3681,8 +4039,13 @@
       <c r="M28" s="7" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="29" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N28" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="O28" s="15"/>
+      <c r="P28" s="15"/>
+    </row>
+    <row r="29" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>102</v>
       </c>
@@ -3708,7 +4071,7 @@
         <v>46</v>
       </c>
       <c r="I29" s="10">
-        <f>IF(OR(E29="",F29=""),"",E29/IF(G29="oz",F29/16,F29))</f>
+        <f t="shared" si="0"/>
         <v>1.6361818181818182</v>
       </c>
       <c r="J29" s="7">
@@ -3723,8 +4086,13 @@
       <c r="M29" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N29" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+    </row>
+    <row r="30" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>103</v>
       </c>
@@ -3750,7 +4118,7 @@
         <v>46</v>
       </c>
       <c r="I30" s="10">
-        <f>IF(OR(E30="",F30=""),"",E30/IF(G30="oz",F30/16,F30))</f>
+        <f t="shared" si="0"/>
         <v>2.69</v>
       </c>
       <c r="J30" s="7">
@@ -3765,8 +4133,13 @@
       <c r="M30" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N30" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+    </row>
+    <row r="31" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>104</v>
       </c>
@@ -3792,7 +4165,7 @@
         <v>46</v>
       </c>
       <c r="I31" s="10">
-        <f>IF(OR(E31="",F31=""),"",E31/IF(G31="oz",F31/16,F31))</f>
+        <f t="shared" si="0"/>
         <v>2.99</v>
       </c>
       <c r="J31" s="7">
@@ -3807,8 +4180,13 @@
       <c r="M31" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N31" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+    </row>
+    <row r="32" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>105</v>
       </c>
@@ -3834,8 +4212,8 @@
         <v>56</v>
       </c>
       <c r="I32" s="10">
-        <f>IF(OR(E32="",F32=""),"",E32/IF(G32="oz",F32/16,F32))</f>
-        <v>2.739</v>
+        <f t="shared" si="0"/>
+        <v>2.7389999999999999</v>
       </c>
       <c r="J32" s="7">
         <v>1</v>
@@ -3849,8 +4227,13 @@
       <c r="M32" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N32" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+    </row>
+    <row r="33" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>106</v>
       </c>
@@ -3864,7 +4247,7 @@
         <v>2</v>
       </c>
       <c r="E33" s="9">
-        <v>79.99</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="F33" s="7">
         <v>55</v>
@@ -3876,7 +4259,7 @@
         <v>46</v>
       </c>
       <c r="I33" s="10">
-        <f>IF(OR(E33="",F33=""),"",E33/IF(G33="oz",F33/16,F33))</f>
+        <f t="shared" si="0"/>
         <v>1.4543636363636363</v>
       </c>
       <c r="J33" s="7">
@@ -3891,8 +4274,13 @@
       <c r="M33" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N33" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+    </row>
+    <row r="34" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>108</v>
       </c>
@@ -3918,7 +4306,7 @@
         <v>46</v>
       </c>
       <c r="I34" s="10">
-        <f>IF(OR(E34="",F34=""),"",E34/IF(G34="oz",F34/16,F34))</f>
+        <f t="shared" si="0"/>
         <v>1.5998181818181818</v>
       </c>
       <c r="J34" s="7">
@@ -3933,8 +4321,13 @@
       <c r="M34" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" ht="41.45" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N34" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+    </row>
+    <row r="35" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>110</v>
       </c>
@@ -3942,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="8">
-        <v>0.135</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="D35" s="7">
         <v>0</v>
@@ -3960,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="I35" s="10">
-        <f>IF(OR(E35="",F35=""),"",E35/IF(G35="oz",F35/16,F35))</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="J35" s="7">
@@ -3975,8 +4368,13 @@
       <c r="M35" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N35" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="O35" s="15"/>
+      <c r="P35" s="15"/>
+    </row>
+    <row r="36" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>112</v>
       </c>
@@ -4002,7 +4400,7 @@
         <v>46</v>
       </c>
       <c r="I36" s="10">
-        <f>IF(OR(E36="",F36=""),"",E36/IF(G36="oz",F36/16,F36))</f>
+        <f t="shared" si="0"/>
         <v>1.79</v>
       </c>
       <c r="J36" s="7">
@@ -4017,8 +4415,13 @@
       <c r="M36" s="7" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="37" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N36" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+    </row>
+    <row r="37" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>115</v>
       </c>
@@ -4044,7 +4447,7 @@
         <v>46</v>
       </c>
       <c r="I37" s="10">
-        <f>IF(OR(E37="",F37=""),"",E37/IF(G37="oz",F37/16,F37))</f>
+        <f t="shared" si="0"/>
         <v>1.99</v>
       </c>
       <c r="J37" s="7">
@@ -4059,8 +4462,13 @@
       <c r="M37" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N37" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+    </row>
+    <row r="38" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>117</v>
       </c>
@@ -4086,7 +4494,7 @@
         <v>118</v>
       </c>
       <c r="I38" s="10" t="str">
-        <f>IF(OR(E38="",F38=""),"",E38/IF(G38="oz",F38/16,F38))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J38" s="7">
@@ -4101,8 +4509,13 @@
       <c r="M38" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N38" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+    </row>
+    <row r="39" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>120</v>
       </c>
@@ -4128,7 +4541,7 @@
         <v>46</v>
       </c>
       <c r="I39" s="10">
-        <f>IF(OR(E39="",F39=""),"",E39/IF(G39="oz",F39/16,F39))</f>
+        <f t="shared" si="0"/>
         <v>2.99</v>
       </c>
       <c r="J39" s="7">
@@ -4143,8 +4556,13 @@
       <c r="M39" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N39" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O39" s="15"/>
+      <c r="P39" s="15"/>
+    </row>
+    <row r="40" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>121</v>
       </c>
@@ -4170,7 +4588,7 @@
         <v>46</v>
       </c>
       <c r="I40" s="10">
-        <f>IF(OR(E40="",F40=""),"",E40/IF(G40="oz",F40/16,F40))</f>
+        <f t="shared" si="0"/>
         <v>1.99</v>
       </c>
       <c r="J40" s="7">
@@ -4185,8 +4603,15 @@
       <c r="M40" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N40" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O40" s="15"/>
+      <c r="P40" s="15">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>123</v>
       </c>
@@ -4212,7 +4637,7 @@
         <v>56</v>
       </c>
       <c r="I41" s="10">
-        <f>IF(OR(E41="",F41=""),"",E41/IF(G41="oz",F41/16,F41))</f>
+        <f t="shared" si="0"/>
         <v>2.79</v>
       </c>
       <c r="J41" s="7">
@@ -4227,8 +4652,15 @@
       <c r="M41" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N41" s="15" t="s">
+        <v>472</v>
+      </c>
+      <c r="O41" s="15"/>
+      <c r="P41" s="15">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>125</v>
       </c>
@@ -4254,7 +4686,7 @@
         <v>46</v>
       </c>
       <c r="I42" s="10">
-        <f>IF(OR(E42="",F42=""),"",E42/IF(G42="oz",F42/16,F42))</f>
+        <f t="shared" si="0"/>
         <v>2.79</v>
       </c>
       <c r="J42" s="7">
@@ -4269,8 +4701,13 @@
       <c r="M42" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" ht="27.6" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N42" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O42" s="15"/>
+      <c r="P42" s="15"/>
+    </row>
+    <row r="43" spans="1:16" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>127</v>
       </c>
@@ -4296,8 +4733,8 @@
         <v>46</v>
       </c>
       <c r="I43" s="10">
-        <f>IF(OR(E43="",F43=""),"",E43/IF(G43="oz",F43/16,F43))</f>
-        <v>0.8454545454545455</v>
+        <f t="shared" si="0"/>
+        <v>0.84545454545454546</v>
       </c>
       <c r="J43" s="7">
         <v>45</v>
@@ -4311,27 +4748,29 @@
       <c r="M43" s="7" t="s">
         <v>128</v>
       </c>
+      <c r="N43" s="15" t="s">
+        <v>471</v>
+      </c>
+      <c r="O43" s="15"/>
+      <c r="P43" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="L10:L44">
-      <formula1>"Check,OK,Confirmed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L44">
+  <autoFilter ref="A1:M1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L44" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Check,OK,Confirmed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -4345,7 +4784,7 @@
     <col min="12" max="12" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.9" customHeight="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="6" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
@@ -4383,7 +4822,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" ht="41.45" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>132</v>
       </c>
@@ -4391,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="8">
-        <v>0.143</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="D2" s="9">
         <v>0</v>
@@ -4406,7 +4845,7 @@
         <v>133</v>
       </c>
       <c r="H2" s="10" t="str">
-        <f>IF(OR(D2="",E2=""),"",D2/(E2*IF(F2="lb",16,1)))</f>
+        <f t="shared" ref="H2:H44" si="0">IF(OR(D2="",E2=""),"",D2/(E2*IF(F2="lb",16,1)))</f>
         <v/>
       </c>
       <c r="I2" s="7">
@@ -4422,7 +4861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>135</v>
       </c>
@@ -4433,7 +4872,7 @@
         <v>0.1</v>
       </c>
       <c r="D3" s="9">
-        <v>18.99</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="E3" s="7">
         <v>1</v>
@@ -4445,8 +4884,8 @@
         <v>136</v>
       </c>
       <c r="H3" s="10">
-        <f>IF(OR(D3="",E3=""),"",D3/(E3*IF(F3="lb",16,1)))</f>
-        <v>1.186875</v>
+        <f t="shared" si="0"/>
+        <v>1.1868749999999999</v>
       </c>
       <c r="I3" s="7">
         <v>45</v>
@@ -4461,7 +4900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>137</v>
       </c>
@@ -4484,7 +4923,7 @@
         <v>136</v>
       </c>
       <c r="H4" s="10">
-        <f>IF(OR(D4="",E4=""),"",D4/(E4*IF(F4="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
       <c r="I4" s="7">
@@ -4500,7 +4939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>140</v>
       </c>
@@ -4508,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="8">
-        <v>0.144</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="D5" s="9">
         <v>9.9</v>
@@ -4523,8 +4962,8 @@
         <v>136</v>
       </c>
       <c r="H5" s="10">
-        <f>IF(OR(D5="",E5=""),"",D5/(E5*IF(F5="lb",16,1)))</f>
-        <v>0.61875</v>
+        <f t="shared" si="0"/>
+        <v>0.61875000000000002</v>
       </c>
       <c r="I5" s="7">
         <v>45</v>
@@ -4539,7 +4978,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="6" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>142</v>
       </c>
@@ -4547,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="8">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D6" s="9">
         <v>9.75</v>
@@ -4562,7 +5001,7 @@
         <v>136</v>
       </c>
       <c r="H6" s="10">
-        <f>IF(OR(D6="",E6=""),"",D6/(E6*IF(F6="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.21875</v>
       </c>
       <c r="I6" s="7">
@@ -4578,7 +5017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>144</v>
       </c>
@@ -4586,7 +5025,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="8">
-        <v>0.062</v>
+        <v>6.2E-2</v>
       </c>
       <c r="D7" s="9">
         <v>10</v>
@@ -4601,7 +5040,7 @@
         <v>136</v>
       </c>
       <c r="H7" s="10">
-        <f>IF(OR(D7="",E7=""),"",D7/(E7*IF(F7="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
       <c r="I7" s="7">
@@ -4617,7 +5056,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="8" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>147</v>
       </c>
@@ -4625,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="8">
-        <v>0.055</v>
+        <v>5.5E-2</v>
       </c>
       <c r="D8" s="9">
         <v>34</v>
@@ -4640,7 +5079,7 @@
         <v>148</v>
       </c>
       <c r="H8" s="10">
-        <f>IF(OR(D8="",E8=""),"",D8/(E8*IF(F8="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>2.125</v>
       </c>
       <c r="I8" s="7">
@@ -4656,7 +5095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>149</v>
       </c>
@@ -4679,7 +5118,7 @@
         <v>136</v>
       </c>
       <c r="H9" s="10">
-        <f>IF(OR(D9="",E9=""),"",D9/(E9*IF(F9="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
       <c r="I9" s="7">
@@ -4695,7 +5134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>150</v>
       </c>
@@ -4703,7 +5142,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="8">
-        <v>0.098</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="D10" s="9">
         <v>12.79</v>
@@ -4718,8 +5157,8 @@
         <v>56</v>
       </c>
       <c r="H10" s="10">
-        <f>IF(OR(D10="",E10=""),"",D10/(E10*IF(F10="lb",16,1)))</f>
-        <v>0.799375</v>
+        <f t="shared" si="0"/>
+        <v>0.79937499999999995</v>
       </c>
       <c r="I10" s="7">
         <v>45</v>
@@ -4734,7 +5173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>151</v>
       </c>
@@ -4757,7 +5196,7 @@
         <v>56</v>
       </c>
       <c r="H11" s="10">
-        <f>IF(OR(D11="",E11=""),"",D11/(E11*IF(F11="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I11" s="7">
@@ -4773,7 +5212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>152</v>
       </c>
@@ -4796,7 +5235,7 @@
         <v>136</v>
       </c>
       <c r="H12" s="10">
-        <f>IF(OR(D12="",E12=""),"",D12/(E12*IF(F12="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.7275</v>
       </c>
       <c r="I12" s="7">
@@ -4812,7 +5251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>153</v>
       </c>
@@ -4820,7 +5259,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="8">
-        <v>0.065</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="D13" s="9">
         <v>3.99</v>
@@ -4835,8 +5274,8 @@
         <v>148</v>
       </c>
       <c r="H13" s="10">
-        <f>IF(OR(D13="",E13=""),"",D13/(E13*IF(F13="lb",16,1)))</f>
-        <v>1.995</v>
+        <f t="shared" si="0"/>
+        <v>1.9950000000000001</v>
       </c>
       <c r="I13" s="7">
         <v>38</v>
@@ -4851,7 +5290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>154</v>
       </c>
@@ -4874,8 +5313,8 @@
         <v>148</v>
       </c>
       <c r="H14" s="10">
-        <f>IF(OR(D14="",E14=""),"",D14/(E14*IF(F14="lb",16,1)))</f>
-        <v>1.343125</v>
+        <f t="shared" si="0"/>
+        <v>1.3431249999999999</v>
       </c>
       <c r="I14" s="7">
         <v>45</v>
@@ -4890,7 +5329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>155</v>
       </c>
@@ -4913,7 +5352,7 @@
         <v>156</v>
       </c>
       <c r="H15" s="10" t="str">
-        <f>IF(OR(D15="",E15=""),"",D15/(E15*IF(F15="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I15" s="7">
@@ -4929,7 +5368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>158</v>
       </c>
@@ -4937,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="8">
-        <v>0.055</v>
+        <v>5.5E-2</v>
       </c>
       <c r="D16" s="9">
         <v>4</v>
@@ -4952,7 +5391,7 @@
         <v>148</v>
       </c>
       <c r="H16" s="10">
-        <f>IF(OR(D16="",E16=""),"",D16/(E16*IF(F16="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I16" s="7">
@@ -4968,7 +5407,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="17" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>160</v>
       </c>
@@ -4976,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="8">
-        <v>0.134</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="D17" s="9">
         <v>15</v>
@@ -4991,7 +5430,7 @@
         <v>136</v>
       </c>
       <c r="H17" s="10">
-        <f>IF(OR(D17="",E17=""),"",D17/(E17*IF(F17="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.9375</v>
       </c>
       <c r="I17" s="7">
@@ -5007,7 +5446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>161</v>
       </c>
@@ -5030,8 +5469,8 @@
         <v>136</v>
       </c>
       <c r="H18" s="10">
-        <f>IF(OR(D18="",E18=""),"",D18/(E18*IF(F18="lb",16,1)))</f>
-        <v>0.936875</v>
+        <f t="shared" si="0"/>
+        <v>0.93687500000000001</v>
       </c>
       <c r="I18" s="7">
         <v>1</v>
@@ -5046,7 +5485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>162</v>
       </c>
@@ -5069,7 +5508,7 @@
         <v>148</v>
       </c>
       <c r="H19" s="10">
-        <f>IF(OR(D19="",E19=""),"",D19/(E19*IF(F19="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I19" s="7">
@@ -5085,7 +5524,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="20" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>164</v>
       </c>
@@ -5108,7 +5547,7 @@
         <v>136</v>
       </c>
       <c r="H20" s="10">
-        <f>IF(OR(D20="",E20=""),"",D20/(E20*IF(F20="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.84375</v>
       </c>
       <c r="I20" s="7">
@@ -5124,7 +5563,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="21" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>167</v>
       </c>
@@ -5147,8 +5586,8 @@
         <v>148</v>
       </c>
       <c r="H21" s="10">
-        <f>IF(OR(D21="",E21=""),"",D21/(E21*IF(F21="lb",16,1)))</f>
-        <v>2.495</v>
+        <f t="shared" si="0"/>
+        <v>2.4950000000000001</v>
       </c>
       <c r="I21" s="7">
         <v>34</v>
@@ -5163,7 +5602,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="22" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>169</v>
       </c>
@@ -5171,7 +5610,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="8">
-        <v>0.029</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="D22" s="9">
         <v>9.75</v>
@@ -5186,7 +5625,7 @@
         <v>136</v>
       </c>
       <c r="H22" s="10">
-        <f>IF(OR(D22="",E22=""),"",D22/(E22*IF(F22="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.21875</v>
       </c>
       <c r="I22" s="7">
@@ -5202,7 +5641,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" ht="41.45" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>171</v>
       </c>
@@ -5225,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="H23" s="10" t="str">
-        <f>IF(OR(D23="",E23=""),"",D23/(E23*IF(F23="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I23" s="7">
@@ -5241,7 +5680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="41.45" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>173</v>
       </c>
@@ -5264,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="10" t="str">
-        <f>IF(OR(D24="",E24=""),"",D24/(E24*IF(F24="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I24" s="7">
@@ -5280,7 +5719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>174</v>
       </c>
@@ -5288,10 +5727,10 @@
         <v>1</v>
       </c>
       <c r="C25" s="8">
-        <v>0.14</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="D25" s="9">
-        <v>18.99</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="E25" s="7">
         <v>1</v>
@@ -5303,8 +5742,8 @@
         <v>136</v>
       </c>
       <c r="H25" s="10">
-        <f>IF(OR(D25="",E25=""),"",D25/(E25*IF(F25="lb",16,1)))</f>
-        <v>1.186875</v>
+        <f t="shared" si="0"/>
+        <v>1.1868749999999999</v>
       </c>
       <c r="I25" s="7">
         <v>45</v>
@@ -5319,7 +5758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>175</v>
       </c>
@@ -5342,8 +5781,8 @@
         <v>148</v>
       </c>
       <c r="H26" s="10">
-        <f>IF(OR(D26="",E26=""),"",D26/(E26*IF(F26="lb",16,1)))</f>
-        <v>1.561875</v>
+        <f t="shared" si="0"/>
+        <v>1.5618749999999999</v>
       </c>
       <c r="I26" s="7">
         <v>45</v>
@@ -5358,7 +5797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>176</v>
       </c>
@@ -5381,7 +5820,7 @@
         <v>136</v>
       </c>
       <c r="H27" s="10">
-        <f>IF(OR(D27="",E27=""),"",D27/(E27*IF(F27="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.9375</v>
       </c>
       <c r="I27" s="7">
@@ -5397,7 +5836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>177</v>
       </c>
@@ -5420,7 +5859,7 @@
         <v>136</v>
       </c>
       <c r="H28" s="10">
-        <f>IF(OR(D28="",E28=""),"",D28/(E28*IF(F28="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.7275</v>
       </c>
       <c r="I28" s="7">
@@ -5436,7 +5875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>178</v>
       </c>
@@ -5444,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="8">
-        <v>0.175</v>
+        <v>0.17499999999999999</v>
       </c>
       <c r="D29" s="9">
         <v>11.75</v>
@@ -5459,7 +5898,7 @@
         <v>136</v>
       </c>
       <c r="H29" s="10">
-        <f>IF(OR(D29="",E29=""),"",D29/(E29*IF(F29="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.734375</v>
       </c>
       <c r="I29" s="7">
@@ -5475,7 +5914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>179</v>
       </c>
@@ -5483,7 +5922,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="8">
-        <v>0.07</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="D30" s="9">
         <v>2</v>
@@ -5498,7 +5937,7 @@
         <v>136</v>
       </c>
       <c r="H30" s="10">
-        <f>IF(OR(D30="",E30=""),"",D30/(E30*IF(F30="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="I30" s="7">
@@ -5514,7 +5953,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" ht="55.15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>181</v>
       </c>
@@ -5522,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="8">
-        <v>0.049</v>
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="D31" s="9">
         <v>2</v>
@@ -5537,7 +5976,7 @@
         <v>136</v>
       </c>
       <c r="H31" s="10">
-        <f>IF(OR(D31="",E31=""),"",D31/(E31*IF(F31="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I31" s="7">
@@ -5553,7 +5992,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="32" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>184</v>
       </c>
@@ -5576,7 +6015,7 @@
         <v>185</v>
       </c>
       <c r="H32" s="10" t="str">
-        <f>IF(OR(D32="",E32=""),"",D32/(E32*IF(F32="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I32" s="7">
@@ -5592,7 +6031,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="33" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>188</v>
       </c>
@@ -5615,7 +6054,7 @@
         <v>136</v>
       </c>
       <c r="H33" s="10">
-        <f>IF(OR(D33="",E33=""),"",D33/(E33*IF(F33="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.6875</v>
       </c>
       <c r="I33" s="7">
@@ -5631,7 +6070,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>190</v>
       </c>
@@ -5639,7 +6078,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="8">
-        <v>0.147</v>
+        <v>0.14699999999999999</v>
       </c>
       <c r="D34" s="9">
         <v>11</v>
@@ -5654,7 +6093,7 @@
         <v>136</v>
       </c>
       <c r="H34" s="10">
-        <f>IF(OR(D34="",E34=""),"",D34/(E34*IF(F34="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.6875</v>
       </c>
       <c r="I34" s="7">
@@ -5670,7 +6109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>191</v>
       </c>
@@ -5678,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="8">
-        <v>0.071</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="D35" s="9">
         <v>15</v>
@@ -5693,7 +6132,7 @@
         <v>136</v>
       </c>
       <c r="H35" s="10">
-        <f>IF(OR(D35="",E35=""),"",D35/(E35*IF(F35="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.9375</v>
       </c>
       <c r="I35" s="7">
@@ -5709,7 +6148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>192</v>
       </c>
@@ -5732,7 +6171,7 @@
         <v>148</v>
       </c>
       <c r="H36" s="10">
-        <f>IF(OR(D36="",E36=""),"",D36/(E36*IF(F36="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I36" s="7">
@@ -5748,7 +6187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>193</v>
       </c>
@@ -5771,7 +6210,7 @@
         <v>148</v>
       </c>
       <c r="H37" s="10">
-        <f>IF(OR(D37="",E37=""),"",D37/(E37*IF(F37="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="I37" s="7">
@@ -5787,7 +6226,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>194</v>
       </c>
@@ -5798,7 +6237,7 @@
         <v>0.123</v>
       </c>
       <c r="D38" s="9">
-        <v>18.99</v>
+        <v>18.989999999999998</v>
       </c>
       <c r="E38" s="7">
         <v>1</v>
@@ -5810,8 +6249,8 @@
         <v>136</v>
       </c>
       <c r="H38" s="10">
-        <f>IF(OR(D38="",E38=""),"",D38/(E38*IF(F38="lb",16,1)))</f>
-        <v>1.186875</v>
+        <f t="shared" si="0"/>
+        <v>1.1868749999999999</v>
       </c>
       <c r="I38" s="7">
         <v>45</v>
@@ -5826,7 +6265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>195</v>
       </c>
@@ -5834,7 +6273,7 @@
         <v>1</v>
       </c>
       <c r="C39" s="8">
-        <v>0.095</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="D39" s="9">
         <v>13</v>
@@ -5849,7 +6288,7 @@
         <v>136</v>
       </c>
       <c r="H39" s="10">
-        <f>IF(OR(D39="",E39=""),"",D39/(E39*IF(F39="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>0.8125</v>
       </c>
       <c r="I39" s="7">
@@ -5865,7 +6304,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="40" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>197</v>
       </c>
@@ -5873,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="8">
-        <v>0.029</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="D40" s="9">
         <v>3.49</v>
@@ -5888,8 +6327,8 @@
         <v>148</v>
       </c>
       <c r="H40" s="10">
-        <f>IF(OR(D40="",E40=""),"",D40/(E40*IF(F40="lb",16,1)))</f>
-        <v>1.745</v>
+        <f t="shared" si="0"/>
+        <v>1.7450000000000001</v>
       </c>
       <c r="I40" s="7">
         <v>1</v>
@@ -5904,7 +6343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>199</v>
       </c>
@@ -5927,7 +6366,7 @@
         <v>56</v>
       </c>
       <c r="H41" s="10">
-        <f>IF(OR(D41="",E41=""),"",D41/(E41*IF(F41="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>2.145</v>
       </c>
       <c r="I41" s="7">
@@ -5943,7 +6382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>200</v>
       </c>
@@ -5966,7 +6405,7 @@
         <v>136</v>
       </c>
       <c r="H42" s="10">
-        <f>IF(OR(D42="",E42=""),"",D42/(E42*IF(F42="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1.87375</v>
       </c>
       <c r="I42" s="7">
@@ -5982,7 +6421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>202</v>
       </c>
@@ -5990,7 +6429,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="8">
-        <v>0.026</v>
+        <v>2.5999999999999999E-2</v>
       </c>
       <c r="D43" s="9">
         <v>6</v>
@@ -6005,7 +6444,7 @@
         <v>203</v>
       </c>
       <c r="H43" s="10">
-        <f>IF(OR(D43="",E43=""),"",D43/(E43*IF(F43="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="I43" s="7">
@@ -6021,7 +6460,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="44" ht="27.6" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>206</v>
       </c>
@@ -6044,7 +6483,7 @@
         <v>136</v>
       </c>
       <c r="H44" s="10">
-        <f>IF(OR(D44="",E44=""),"",D44/(E44*IF(F44="lb",16,1)))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="I44" s="7">
@@ -6061,25 +6500,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="K10:K44">
-      <formula1>"Check,OK,Confirmed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K44">
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K44" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Check,OK,Confirmed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -6093,7 +6529,7 @@
     <col min="12" max="12" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.9" customHeight="1" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="6" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>31</v>
       </c>
@@ -6131,7 +6567,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>216</v>
       </c>
@@ -6169,7 +6605,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="3" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>222</v>
       </c>
@@ -6207,7 +6643,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" ht="43.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>226</v>
       </c>
@@ -6245,7 +6681,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>230</v>
       </c>
@@ -6283,7 +6719,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>234</v>
       </c>
@@ -6319,7 +6755,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="7" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>238</v>
       </c>
@@ -6357,7 +6793,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>241</v>
       </c>
@@ -6393,7 +6829,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="9" ht="57.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>245</v>
       </c>
@@ -6431,7 +6867,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="10" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>249</v>
       </c>
@@ -6469,7 +6905,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="11" ht="57.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>252</v>
       </c>
@@ -6507,7 +6943,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" ht="57.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>257</v>
       </c>
@@ -6545,7 +6981,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="13" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>261</v>
       </c>
@@ -6583,7 +7019,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="14" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>264</v>
       </c>
@@ -6621,7 +7057,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="15" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>267</v>
       </c>
@@ -6659,7 +7095,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="16" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>270</v>
       </c>
@@ -6697,7 +7133,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="17" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>273</v>
       </c>
@@ -6735,7 +7171,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>278</v>
       </c>
@@ -6773,7 +7209,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="19" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>281</v>
       </c>
@@ -6811,7 +7247,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>284</v>
       </c>
@@ -6847,7 +7283,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="21" ht="43.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>288</v>
       </c>
@@ -6885,7 +7321,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="22" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>292</v>
       </c>
@@ -6923,7 +7359,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="23" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>295</v>
       </c>
@@ -6961,7 +7397,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="24" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>298</v>
       </c>
@@ -6999,7 +7435,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="25" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>302</v>
       </c>
@@ -7037,7 +7473,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="26" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>305</v>
       </c>
@@ -7075,7 +7511,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="27" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>309</v>
       </c>
@@ -7113,7 +7549,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="28" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>312</v>
       </c>
@@ -7151,7 +7587,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="29" ht="28.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>315</v>
       </c>
@@ -7189,7 +7625,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="30" ht="14.25" customHeight="1" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>320</v>
       </c>
@@ -7224,7 +7660,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="31" ht="14.25" customHeight="1" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>325</v>
       </c>
@@ -7259,7 +7695,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" ht="14.25" customHeight="1" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
         <v>328</v>
       </c>
@@ -7294,7 +7730,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="33" ht="14.25" customHeight="1" spans="1:12" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" s="11" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>331</v>
       </c>
@@ -7330,31 +7766,25 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
-  <dataValidations count="4">
-    <dataValidation type="list" sqref="D10:D29">
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="D2:D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Ale,Lager"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D2:D29">
-      <formula1>"Ale,Lager"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K10:K33">
-      <formula1>"Check,OK,Confirmed"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K33">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K33" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"Check,OK,Confirmed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -7363,7 +7793,7 @@
     <col min="5" max="5" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.9" customHeight="1" spans="1:5" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="6" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>334</v>
       </c>
@@ -7380,7 +7810,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" ht="27.6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>337</v>
       </c>
@@ -7392,13 +7822,13 @@
       </c>
       <c r="D2" s="13">
         <f>IF(OR(B2="",C2=""),"",B2/C2)</f>
-        <v>0.06495000000000001</v>
+        <v>6.4950000000000008E-2</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="3" ht="27.6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>339</v>
       </c>
@@ -7416,7 +7846,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="4" ht="27.6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>340</v>
       </c>
@@ -7428,13 +7858,13 @@
       </c>
       <c r="D4" s="13">
         <f>IF(OR(B4="",C4=""),"",B4/C4)</f>
-        <v>0.07475</v>
+        <v>7.4749999999999997E-2</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="5" ht="27.6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>341</v>
       </c>
@@ -7446,13 +7876,13 @@
       </c>
       <c r="D5" s="13">
         <f>IF(OR(B5="",C5=""),"",B5/C5)</f>
-        <v>0.06495000000000001</v>
+        <v>6.4950000000000008E-2</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="6" ht="27.6" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>342</v>
       </c>
@@ -7464,24 +7894,24 @@
       </c>
       <c r="D6" s="13">
         <f>IF(OR(B6="",C6=""),"",B6/C6)</f>
-        <v>0.075</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>338</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F45"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -7491,7 +7921,7 @@
     <col min="6" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.9" customHeight="1" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="6" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>343</v>
       </c>
@@ -7511,7 +7941,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="2" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>348</v>
       </c>
@@ -7531,7 +7961,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="3" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>348</v>
       </c>
@@ -7551,7 +7981,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="4" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>348</v>
       </c>
@@ -7571,7 +8001,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="5" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>348</v>
       </c>
@@ -7591,7 +8021,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="6" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>348</v>
       </c>
@@ -7611,7 +8041,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="7" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>348</v>
       </c>
@@ -7631,7 +8061,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" ht="41.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>348</v>
       </c>
@@ -7651,7 +8081,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="9" ht="41.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>348</v>
       </c>
@@ -7671,7 +8101,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="10" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>348</v>
       </c>
@@ -7691,7 +8121,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="11" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>348</v>
       </c>
@@ -7711,7 +8141,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="12" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>348</v>
       </c>
@@ -7731,7 +8161,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="13" ht="55.15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>348</v>
       </c>
@@ -7751,7 +8181,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="14" ht="55.15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>348</v>
       </c>
@@ -7771,7 +8201,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="15" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>348</v>
       </c>
@@ -7791,7 +8221,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="16" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>348</v>
       </c>
@@ -7811,7 +8241,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="17" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>348</v>
       </c>
@@ -7831,7 +8261,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="18" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>394</v>
       </c>
@@ -7851,7 +8281,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="19" ht="55.15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>394</v>
       </c>
@@ -7871,7 +8301,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="20" ht="41.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>394</v>
       </c>
@@ -7891,7 +8321,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="21" ht="55.15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>394</v>
       </c>
@@ -7911,7 +8341,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="22" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>394</v>
       </c>
@@ -7931,7 +8361,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="23" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>394</v>
       </c>
@@ -7951,7 +8381,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="24" ht="41.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>394</v>
       </c>
@@ -7971,7 +8401,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="25" ht="41.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>394</v>
       </c>
@@ -7991,7 +8421,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="26" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>394</v>
       </c>
@@ -8011,7 +8441,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="27" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>394</v>
       </c>
@@ -8031,7 +8461,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="28" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>394</v>
       </c>
@@ -8051,7 +8481,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>394</v>
       </c>
@@ -8071,7 +8501,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="30" ht="41.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>394</v>
       </c>
@@ -8091,7 +8521,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="31" ht="41.45" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>394</v>
       </c>
@@ -8111,7 +8541,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="32" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>394</v>
       </c>
@@ -8131,7 +8561,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="33" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>394</v>
       </c>
@@ -8151,7 +8581,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="34" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>394</v>
       </c>
@@ -8171,7 +8601,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="35" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>441</v>
       </c>
@@ -8191,7 +8621,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="36" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>441</v>
       </c>
@@ -8211,7 +8641,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="37" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>441</v>
       </c>
@@ -8231,7 +8661,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="38" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>441</v>
       </c>
@@ -8251,7 +8681,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>441</v>
       </c>
@@ -8271,7 +8701,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="40" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>441</v>
       </c>
@@ -8291,7 +8721,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="41" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>441</v>
       </c>
@@ -8311,7 +8741,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>441</v>
       </c>
@@ -8331,7 +8761,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="43" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>441</v>
       </c>
@@ -8351,7 +8781,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="44" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>441</v>
       </c>
@@ -8371,7 +8801,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="45" ht="27.6" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>441</v>
       </c>
@@ -8392,174 +8822,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="26.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" ht="26.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="39.6" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="39.6" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" ht="26.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" ht="26.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" ht="26.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" ht="26.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" ht="26.45" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>